--- a/GERADOR DE DOCUMENTOS/SCRIPTS/Planilha_Municipios.xlsx
+++ b/GERADOR DE DOCUMENTOS/SCRIPTS/Planilha_Municipios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuário 1\Documents\Inovve_Automação\GERADOR DE DOCUMENTOS\SCRIPTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07DA61BB-0A8F-42B6-95F9-D5713240E2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B048A7-2352-48E6-8D9C-77DAA9F7900D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="751">
   <si>
     <t>_arquivo_origem</t>
   </si>
@@ -2311,6 +2311,18 @@
   </si>
   <si>
     <t>Input</t>
+  </si>
+  <si>
+    <t>(83) 3373-1010</t>
+  </si>
+  <si>
+    <t>controladoria@araruna.pb.gov.br</t>
+  </si>
+  <si>
+    <t>(83) 3113-0142</t>
+  </si>
+  <si>
+    <t>lai@salgadosaofelix.pb.gov.br</t>
   </si>
 </sst>
 </file>
@@ -2419,12 +2431,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <alignment horizontal="general" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <border outline="0">
         <top style="thin">
@@ -2482,14 +2502,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45DA9007-596B-43A6-9D7A-0553BDA4EA40}" name="Tabela1" displayName="Tabela1" ref="A1:S70" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:S70" xr:uid="{45DA9007-596B-43A6-9D7A-0553BDA4EA40}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="ABEL"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{45DA9007-596B-43A6-9D7A-0553BDA4EA40}" name="Tabela1" displayName="Tabela1" ref="A1:S70" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:S70" xr:uid="{45DA9007-596B-43A6-9D7A-0553BDA4EA40}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S49">
     <sortCondition ref="D1:D49"/>
   </sortState>
@@ -2507,8 +2521,8 @@
     <tableColumn id="9" xr3:uid="{3792BD83-47DF-48DA-AC7F-DF94CABE0152}" name="nomePrefeito"/>
     <tableColumn id="8" xr3:uid="{F1648390-6D75-4F26-A001-7244D34704F9}" name="generoPrefeitura"/>
     <tableColumn id="10" xr3:uid="{01D61976-D043-4063-B3AA-56483B40B106}" name="numeroContrato"/>
-    <tableColumn id="11" xr3:uid="{1D693858-9B64-4E35-8721-A1AFBD39E276}" name="quantidadeAditivos"/>
-    <tableColumn id="12" xr3:uid="{8CEE7839-0AE1-4619-952A-C7FAB58D5460}" name="legitimidade"/>
+    <tableColumn id="11" xr3:uid="{1D693858-9B64-4E35-8721-A1AFBD39E276}" name="quantidadeAditivos" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{8CEE7839-0AE1-4619-952A-C7FAB58D5460}" name="legitimidade" dataDxfId="0"/>
     <tableColumn id="13" xr3:uid="{AE09504F-094C-45EF-A2E9-FEAB73828636}" name="publicacao"/>
     <tableColumn id="14" xr3:uid="{E436E158-4E66-408B-80C6-86E58B7ABFA1}" name="dataPublicacao"/>
     <tableColumn id="15" xr3:uid="{8A7F4199-832A-4DDD-B46F-61A5A54D9A26}" name="tituloClausula"/>
@@ -2815,13 +2829,13 @@
     <col min="5" max="5" width="5.77734375" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5546875" customWidth="1"/>
-    <col min="9" max="9" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="25.5546875" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
     <col min="12" max="12" width="17.109375" customWidth="1"/>
     <col min="14" max="14" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.33203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="19.33203125" customWidth="1"/>
     <col min="16" max="16" width="13.21875" customWidth="1"/>
     <col min="17" max="17" width="29.33203125" customWidth="1"/>
     <col min="18" max="18" width="21.44140625" bestFit="1" customWidth="1"/>
@@ -2869,10 +2883,10 @@
       <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="10" t="s">
         <v>11</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -2888,7 +2902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:19" hidden="1">
+    <row r="2" spans="1:19">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -2941,7 +2955,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="3" spans="1:19" hidden="1">
+    <row r="3" spans="1:19">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -2962,6 +2976,12 @@
       </c>
       <c r="G3" t="s">
         <v>152</v>
+      </c>
+      <c r="H3" t="s">
+        <v>747</v>
+      </c>
+      <c r="I3" t="s">
+        <v>748</v>
       </c>
       <c r="J3" t="s">
         <v>200</v>
@@ -3034,10 +3054,10 @@
       <c r="M4" t="s">
         <v>297</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" t="s">
         <v>344</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="O4" t="s">
         <v>343</v>
       </c>
       <c r="P4" t="s">
@@ -3053,7 +3073,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="5" spans="1:19" hidden="1">
+    <row r="5" spans="1:19">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -3146,10 +3166,10 @@
       <c r="M6" t="s">
         <v>299</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" t="s">
         <v>343</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="O6" t="s">
         <v>348</v>
       </c>
       <c r="P6" t="s">
@@ -3165,7 +3185,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="1:19" hidden="1">
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -3218,7 +3238,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:19" hidden="1">
+    <row r="8" spans="1:19">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -3271,7 +3291,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="9" spans="1:19" hidden="1">
+    <row r="9" spans="1:19">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -3324,7 +3344,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="10" spans="1:19" hidden="1">
+    <row r="10" spans="1:19">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -3377,7 +3397,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="11" spans="1:19" hidden="1">
+    <row r="11" spans="1:19">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -3430,7 +3450,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="12" spans="1:19" hidden="1">
+    <row r="12" spans="1:19">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -3483,7 +3503,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="13" spans="1:19" hidden="1">
+    <row r="13" spans="1:19">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -3542,7 +3562,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="14" spans="1:19" hidden="1">
+    <row r="14" spans="1:19">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -3601,7 +3621,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="15" spans="1:19" hidden="1">
+    <row r="15" spans="1:19">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -3694,10 +3714,10 @@
       <c r="M16" t="s">
         <v>309</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="N16" t="s">
         <v>345</v>
       </c>
-      <c r="O16" s="3" t="s">
+      <c r="O16" t="s">
         <v>346</v>
       </c>
       <c r="P16" t="s">
@@ -3713,7 +3733,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:19" hidden="1">
+    <row r="17" spans="1:19">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -3750,7 +3770,6 @@
       <c r="N17" t="s">
         <v>344</v>
       </c>
-      <c r="O17"/>
       <c r="P17" t="s">
         <v>357</v>
       </c>
@@ -3804,10 +3823,10 @@
       <c r="M18" t="s">
         <v>311</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="N18" t="s">
         <v>346</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="O18" t="s">
         <v>343</v>
       </c>
       <c r="P18" t="s">
@@ -3823,7 +3842,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="19" spans="1:19" hidden="1">
+    <row r="19" spans="1:19">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -3916,10 +3935,10 @@
       <c r="M20" t="s">
         <v>313</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="N20" t="s">
         <v>344</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="O20" t="s">
         <v>348</v>
       </c>
       <c r="P20" t="s">
@@ -3935,7 +3954,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="21" spans="1:19" hidden="1">
+    <row r="21" spans="1:19">
       <c r="A21" t="s">
         <v>37</v>
       </c>
@@ -3988,7 +4007,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="22" spans="1:19" hidden="1">
+    <row r="22" spans="1:19">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -4047,7 +4066,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="23" spans="1:19" hidden="1">
+    <row r="23" spans="1:19">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -4106,7 +4125,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="24" spans="1:19" hidden="1">
+    <row r="24" spans="1:19">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -4159,7 +4178,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="25" spans="1:19" hidden="1">
+    <row r="25" spans="1:19">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -4212,7 +4231,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="26" spans="1:19" hidden="1">
+    <row r="26" spans="1:19">
       <c r="A26" t="s">
         <v>42</v>
       </c>
@@ -4265,7 +4284,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="27" spans="1:19" hidden="1">
+    <row r="27" spans="1:19">
       <c r="A27" t="s">
         <v>43</v>
       </c>
@@ -4318,7 +4337,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="28" spans="1:19" hidden="1">
+    <row r="28" spans="1:19">
       <c r="A28" t="s">
         <v>44</v>
       </c>
@@ -4417,10 +4436,10 @@
       <c r="M29" t="s">
         <v>322</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="N29" t="s">
         <v>343</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="O29" t="s">
         <v>343</v>
       </c>
       <c r="P29" t="s">
@@ -4436,7 +4455,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="30" spans="1:19" hidden="1">
+    <row r="30" spans="1:19">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -4489,7 +4508,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="31" spans="1:19" hidden="1">
+    <row r="31" spans="1:19">
       <c r="A31" t="s">
         <v>47</v>
       </c>
@@ -4542,7 +4561,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="32" spans="1:19" hidden="1">
+    <row r="32" spans="1:19">
       <c r="A32" t="s">
         <v>49</v>
       </c>
@@ -4601,7 +4620,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="33" spans="1:19" hidden="1">
+    <row r="33" spans="1:19">
       <c r="A33" t="s">
         <v>48</v>
       </c>
@@ -4654,7 +4673,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="34" spans="1:19" hidden="1">
+    <row r="34" spans="1:19">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -4707,7 +4726,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="35" spans="1:19" hidden="1">
+    <row r="35" spans="1:19">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -4760,7 +4779,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="36" spans="1:19" hidden="1">
+    <row r="36" spans="1:19">
       <c r="A36" t="s">
         <v>52</v>
       </c>
@@ -4782,6 +4801,12 @@
       <c r="G36" t="s">
         <v>185</v>
       </c>
+      <c r="H36" t="s">
+        <v>749</v>
+      </c>
+      <c r="I36" t="s">
+        <v>750</v>
+      </c>
       <c r="J36" t="s">
         <v>232</v>
       </c>
@@ -4813,7 +4838,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="37" spans="1:19" hidden="1">
+    <row r="37" spans="1:19">
       <c r="A37" t="s">
         <v>53</v>
       </c>
@@ -4906,10 +4931,10 @@
       <c r="M38" t="s">
         <v>331</v>
       </c>
-      <c r="N38" s="3" t="s">
+      <c r="N38" t="s">
         <v>347</v>
       </c>
-      <c r="O38" s="3" t="s">
+      <c r="O38" t="s">
         <v>345</v>
       </c>
       <c r="P38" t="s">
@@ -4925,7 +4950,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="39" spans="1:19" hidden="1">
+    <row r="39" spans="1:19">
       <c r="A39" t="s">
         <v>58</v>
       </c>
@@ -4978,7 +5003,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="40" spans="1:19" hidden="1">
+    <row r="40" spans="1:19">
       <c r="A40" t="s">
         <v>59</v>
       </c>
@@ -5031,7 +5056,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1">
+    <row r="41" spans="1:19">
       <c r="A41" t="s">
         <v>63</v>
       </c>
@@ -5084,7 +5109,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="42" spans="1:19" hidden="1">
+    <row r="42" spans="1:19">
       <c r="A42" t="s">
         <v>60</v>
       </c>
@@ -5137,7 +5162,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="43" spans="1:19" hidden="1">
+    <row r="43" spans="1:19">
       <c r="A43" t="s">
         <v>61</v>
       </c>
@@ -5190,7 +5215,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="44" spans="1:19" hidden="1">
+    <row r="44" spans="1:19">
       <c r="A44" t="s">
         <v>62</v>
       </c>
@@ -5249,7 +5274,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="45" spans="1:19" hidden="1">
+    <row r="45" spans="1:19">
       <c r="A45" t="s">
         <v>55</v>
       </c>
@@ -5302,7 +5327,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="46" spans="1:19" hidden="1">
+    <row r="46" spans="1:19">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -5355,7 +5380,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="47" spans="1:19" hidden="1">
+    <row r="47" spans="1:19">
       <c r="A47" t="s">
         <v>57</v>
       </c>
@@ -5408,7 +5433,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="48" spans="1:19" hidden="1">
+    <row r="48" spans="1:19">
       <c r="A48" t="s">
         <v>64</v>
       </c>
@@ -5461,7 +5486,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1">
+    <row r="49" spans="1:19">
       <c r="A49" t="s">
         <v>65</v>
       </c>
@@ -5554,10 +5579,10 @@
       <c r="M50" t="s">
         <v>650</v>
       </c>
-      <c r="N50" s="3">
+      <c r="N50">
         <v>1</v>
       </c>
-      <c r="O50" s="3">
+      <c r="O50">
         <v>1</v>
       </c>
       <c r="P50" t="s">
@@ -5613,10 +5638,10 @@
       <c r="M51" t="s">
         <v>655</v>
       </c>
-      <c r="N51" s="3">
+      <c r="N51">
         <v>0</v>
       </c>
-      <c r="O51" s="3" t="s">
+      <c r="O51" t="s">
         <v>348</v>
       </c>
       <c r="P51" t="s">
@@ -5672,10 +5697,10 @@
       <c r="M52" t="s">
         <v>659</v>
       </c>
-      <c r="N52" s="3">
+      <c r="N52">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
+      <c r="O52" t="s">
         <v>348</v>
       </c>
       <c r="P52" t="s">
@@ -5731,10 +5756,10 @@
       <c r="M53" t="s">
         <v>662</v>
       </c>
-      <c r="N53" s="3">
+      <c r="N53">
         <v>1</v>
       </c>
-      <c r="O53" s="3">
+      <c r="O53">
         <v>1</v>
       </c>
       <c r="P53" t="s">
@@ -5790,10 +5815,10 @@
       <c r="M54" t="s">
         <v>666</v>
       </c>
-      <c r="N54" s="3">
+      <c r="N54">
         <v>0</v>
       </c>
-      <c r="O54" s="3" t="s">
+      <c r="O54" t="s">
         <v>348</v>
       </c>
       <c r="P54" t="s">
@@ -5849,10 +5874,10 @@
       <c r="M55" t="s">
         <v>672</v>
       </c>
-      <c r="N55" s="3">
+      <c r="N55">
         <v>2</v>
       </c>
-      <c r="O55" s="3">
+      <c r="O55">
         <v>1</v>
       </c>
       <c r="P55" t="s">
@@ -5908,10 +5933,10 @@
       <c r="M56" t="s">
         <v>676</v>
       </c>
-      <c r="N56" s="3">
+      <c r="N56">
         <v>0</v>
       </c>
-      <c r="O56" s="3" t="s">
+      <c r="O56" t="s">
         <v>348</v>
       </c>
       <c r="P56" t="s">
@@ -5967,10 +5992,10 @@
       <c r="M57" t="s">
         <v>680</v>
       </c>
-      <c r="N57" s="3">
+      <c r="N57">
         <v>2</v>
       </c>
-      <c r="O57" s="3">
+      <c r="O57">
         <v>1</v>
       </c>
       <c r="P57" t="s">
@@ -6026,10 +6051,10 @@
       <c r="M58" t="s">
         <v>684</v>
       </c>
-      <c r="N58" s="3">
+      <c r="N58">
         <v>1</v>
       </c>
-      <c r="O58" s="3">
+      <c r="O58">
         <v>1</v>
       </c>
       <c r="P58" t="s">
@@ -6085,10 +6110,10 @@
       <c r="M59" t="s">
         <v>689</v>
       </c>
-      <c r="N59" s="3">
+      <c r="N59">
         <v>1</v>
       </c>
-      <c r="O59" s="3">
+      <c r="O59">
         <v>1</v>
       </c>
       <c r="P59" t="s">
@@ -6144,10 +6169,10 @@
       <c r="M60" t="s">
         <v>693</v>
       </c>
-      <c r="N60" s="3">
+      <c r="N60">
         <v>1</v>
       </c>
-      <c r="O60" s="3">
+      <c r="O60">
         <v>1</v>
       </c>
       <c r="P60" t="s">
@@ -6203,10 +6228,10 @@
       <c r="M61" t="s">
         <v>696</v>
       </c>
-      <c r="N61" s="3">
+      <c r="N61">
         <v>1</v>
       </c>
-      <c r="O61" s="3">
+      <c r="O61">
         <v>1</v>
       </c>
       <c r="P61" t="s">
@@ -6262,10 +6287,10 @@
       <c r="M62" t="s">
         <v>700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="N62">
         <v>1</v>
       </c>
-      <c r="O62" s="3" t="s">
+      <c r="O62" t="s">
         <v>348</v>
       </c>
       <c r="P62" t="s">
@@ -6321,10 +6346,10 @@
       <c r="M63" t="s">
         <v>706</v>
       </c>
-      <c r="N63" s="3">
+      <c r="N63">
         <v>1</v>
       </c>
-      <c r="O63" s="3">
+      <c r="O63">
         <v>1</v>
       </c>
       <c r="P63" t="s">
@@ -6359,7 +6384,7 @@
       <c r="F64" s="7">
         <v>5836772</v>
       </c>
-      <c r="G64" s="10" t="s">
+      <c r="G64" t="s">
         <v>604</v>
       </c>
       <c r="H64" t="s">
@@ -6380,10 +6405,10 @@
       <c r="M64" t="s">
         <v>710</v>
       </c>
-      <c r="N64" s="3">
+      <c r="N64">
         <v>1</v>
       </c>
-      <c r="O64" s="3">
+      <c r="O64">
         <v>1</v>
       </c>
       <c r="P64" t="s">
@@ -6439,10 +6464,10 @@
       <c r="M65" t="s">
         <v>715</v>
       </c>
-      <c r="N65" s="3">
+      <c r="N65">
         <v>2</v>
       </c>
-      <c r="O65" s="3" t="s">
+      <c r="O65" t="s">
         <v>348</v>
       </c>
       <c r="P65" t="s">
@@ -6498,10 +6523,10 @@
       <c r="M66" t="s">
         <v>719</v>
       </c>
-      <c r="N66" s="3">
+      <c r="N66">
         <v>1</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66">
         <v>1</v>
       </c>
       <c r="P66" t="s">
@@ -6557,10 +6582,10 @@
       <c r="M67" t="s">
         <v>722</v>
       </c>
-      <c r="N67" s="3">
+      <c r="N67">
         <v>1</v>
       </c>
-      <c r="O67" s="3">
+      <c r="O67">
         <v>1</v>
       </c>
       <c r="P67" t="s">
@@ -6616,10 +6641,10 @@
       <c r="M68" t="s">
         <v>726</v>
       </c>
-      <c r="N68" s="3">
+      <c r="N68">
         <v>0</v>
       </c>
-      <c r="O68" s="3" t="s">
+      <c r="O68" t="s">
         <v>348</v>
       </c>
       <c r="P68" t="s">
@@ -6675,10 +6700,10 @@
       <c r="M69" t="s">
         <v>730</v>
       </c>
-      <c r="N69" s="3">
+      <c r="N69">
         <v>0</v>
       </c>
-      <c r="O69" s="3" t="s">
+      <c r="O69" t="s">
         <v>348</v>
       </c>
       <c r="P69" t="s">
@@ -6734,10 +6759,10 @@
       <c r="M70">
         <v>20250252</v>
       </c>
-      <c r="N70" s="3">
+      <c r="N70">
         <v>0</v>
       </c>
-      <c r="O70" s="3" t="s">
+      <c r="O70" t="s">
         <v>348</v>
       </c>
       <c r="P70" t="s">
